--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thaddenschulede-my.sharepoint.com/personal/lepold_thaddenschule_de/Documents/09 Musik/2025 Elisabeth/alt/Webseite/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{3028552A-8752-4668-BCF5-26AD18D9605D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17F97B5E-C7A0-4DB4-87A7-31812DE717BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F445666-B333-4F32-AB79-C799E16CBA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,6 @@
     <t>3.3</t>
   </si>
   <si>
-    <t>3.4</t>
-  </si>
-  <si>
     <t>Schauspiel</t>
   </si>
   <si>
@@ -332,7 +329,10 @@
     <t> Eine Heldin A</t>
   </si>
   <si>
-    <t> Eine Heldin B</t>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>Kann Schule neutral sein?</t>
   </si>
 </sst>
 </file>
@@ -450,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -476,6 +476,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -811,22 +812,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -840,10 +841,10 @@
         <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>2</v>
@@ -873,7 +874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -887,7 +888,7 @@
       <c r="G2" s="7"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -898,13 +899,13 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -918,7 +919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -929,7 +930,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -938,7 +939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -949,7 +950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -964,7 +965,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="7"/>
       <c r="J7" s="8"/>
@@ -973,12 +974,12 @@
       </c>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>70</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>71</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>21</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="E8" s="21"/>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>21</v>
@@ -1009,7 +1010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -1026,7 +1027,7 @@
       <c r="J9" s="17"/>
       <c r="O9" s="16"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1037,15 +1038,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>21</v>
@@ -1060,7 +1061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1071,89 +1072,82 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" t="s">
+    <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="G13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="O13" s="7"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="G14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="O14" s="7"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F15" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="J16" s="8"/>
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="1" t="s">
         <v>21</v>
       </c>
@@ -1161,43 +1155,41 @@
       <c r="J17" s="8"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G18" s="7"/>
       <c r="J18" s="8"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="1" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="G19" s="7"/>
-      <c r="J19" s="8"/>
-      <c r="O19" s="7"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>21</v>
@@ -1205,168 +1197,187 @@
       <c r="E20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="F20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L20" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="G21" s="19"/>
+      <c r="J21" s="20"/>
+      <c r="O21" s="19"/>
+    </row>
+    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>94</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>92</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="20"/>
-      <c r="G22" s="19"/>
-      <c r="J22" s="20"/>
-      <c r="O22" s="19"/>
-    </row>
-    <row r="23" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="J23" s="8"/>
-      <c r="O23" s="7"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>95</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>93</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G27" s="7"/>
+      <c r="I27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="L27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
@@ -1375,36 +1386,21 @@
       <c r="E28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="G28" s="7"/>
-      <c r="I28" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="J28" s="8"/>
-      <c r="L28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8" t="s">
-        <v>21</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="8"/>
       <c r="E29" s="1" t="s">
         <v>21</v>
       </c>
@@ -1412,62 +1408,67 @@
       <c r="J29" s="8"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="7"/>
       <c r="J30" s="8"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="1" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="7"/>
-      <c r="J31" s="8"/>
-      <c r="O31" s="7"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>66</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" t="s">
-        <v>69</v>
-      </c>
       <c r="D33" s="10" t="s">
         <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>21</v>
@@ -1491,12 +1492,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>21</v>
@@ -1508,57 +1509,57 @@
       <c r="J34" s="8"/>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
         <v>79</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" t="s">
-        <v>80</v>
-      </c>
-      <c r="F36" t="s">
-        <v>92</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="D37" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>75</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>76</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
@@ -1570,7 +1571,7 @@
         <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L38" t="s">
         <v>21</v>
@@ -1582,45 +1583,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>82</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="8"/>
       <c r="F41" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>21</v>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F445666-B333-4F32-AB79-C799E16CBA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069BBB26-930A-414B-A746-8ECF3B83E6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
   <si>
     <t>Szene</t>
   </si>
@@ -149,12 +149,6 @@
     <t>Irgendwo auf der Welt</t>
   </si>
   <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schulinspektion </t>
   </si>
   <si>
@@ -302,9 +296,6 @@
     <t> Gemeinschaft: Heute</t>
   </si>
   <si>
-    <t> Gemeinschaft: Damals</t>
-  </si>
-  <si>
     <t>Musikalische Leitung</t>
   </si>
   <si>
@@ -333,6 +324,15 @@
   </si>
   <si>
     <t>Kann Schule neutral sein?</t>
+  </si>
+  <si>
+    <t> Schlafsall Damals</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>6.2</t>
   </si>
 </sst>
 </file>
@@ -450,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -477,6 +477,8 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -814,6 +816,7 @@
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.5546875" style="25"/>
     <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
@@ -828,7 +831,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -844,7 +847,7 @@
         <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>2</v>
@@ -875,7 +878,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -889,7 +892,7 @@
       <c r="O2" s="7"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
@@ -899,14 +902,14 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
@@ -920,7 +923,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
@@ -930,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -940,7 +943,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
@@ -951,7 +954,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="26" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -965,7 +968,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G7" s="7"/>
       <c r="J7" s="8"/>
@@ -975,11 +978,11 @@
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>69</v>
+      <c r="A8" s="25" t="s">
+        <v>67</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>21</v>
@@ -989,7 +992,7 @@
       </c>
       <c r="E8" s="21"/>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>21</v>
@@ -1011,7 +1014,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="26" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1028,7 +1031,7 @@
       <c r="O9" s="16"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B10" t="s">
@@ -1039,14 +1042,14 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="25" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>21</v>
@@ -1062,7 +1065,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="25" t="s">
         <v>32</v>
       </c>
       <c r="B12" t="s">
@@ -1072,95 +1075,93 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="J14" s="8"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="G13" s="7"/>
-      <c r="J13" s="8"/>
-      <c r="O13" s="7"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+      <c r="G15" s="7"/>
+      <c r="J15" s="8"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="C17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B18" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="J16" s="8"/>
-      <c r="O16" s="7"/>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="J17" s="8"/>
-      <c r="O17" s="7"/>
-    </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>21</v>
@@ -1171,48 +1172,48 @@
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="C20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>94</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>46</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
@@ -1221,11 +1222,11 @@
       <c r="O21" s="19"/>
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>47</v>
+      <c r="A22" s="26" t="s">
+        <v>45</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="8" t="s">
@@ -1236,115 +1237,115 @@
       <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>91</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>94</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="D24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="D25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>89</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>92</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="D26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8" t="s">
@@ -1354,7 +1355,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G27" s="7"/>
       <c r="I27" s="1" t="s">
@@ -1373,11 +1374,11 @@
       <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>59</v>
+      <c r="A28" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
@@ -1391,11 +1392,11 @@
       <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>61</v>
+      <c r="A29" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>21</v>
@@ -1409,11 +1410,11 @@
       <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>63</v>
+      <c r="A30" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
@@ -1424,25 +1425,25 @@
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
         <v>65</v>
       </c>
-      <c r="B31" t="s">
-        <v>67</v>
-      </c>
       <c r="D31" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>66</v>
+      <c r="A32" s="25" t="s">
+        <v>64</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>21</v>
@@ -1459,16 +1460,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>21</v>
@@ -1493,11 +1494,11 @@
       </c>
     </row>
     <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34" s="26">
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>21</v>
@@ -1510,56 +1511,56 @@
       <c r="O34" s="7"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>78</v>
+      <c r="A35" s="25" t="s">
+        <v>76</v>
       </c>
       <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="F36" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>74</v>
-      </c>
       <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
         <v>73</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>75</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
@@ -1571,7 +1572,7 @@
         <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L38" t="s">
         <v>21</v>
@@ -1584,44 +1585,44 @@
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>76</v>
+      <c r="A39" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="D40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="8"/>
       <c r="F41" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>21</v>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069BBB26-930A-414B-A746-8ECF3B83E6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AA5746-B9BD-436D-A158-71B6ED9CF5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -814,23 +814,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="25"/>
-    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="25"/>
+    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -877,7 +877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>12</v>
       </c>
@@ -891,7 +891,7 @@
       <c r="G2" s="7"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>13</v>
       </c>
@@ -908,7 +908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>17</v>
       </c>
@@ -922,7 +922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>18</v>
       </c>
@@ -942,7 +942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>19</v>
       </c>
@@ -953,7 +953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>22</v>
       </c>
@@ -977,7 +977,7 @@
       </c>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>67</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>24</v>
       </c>
@@ -1030,7 +1030,7 @@
       <c r="J9" s="17"/>
       <c r="O9" s="16"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>28</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>29</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>32</v>
       </c>
@@ -1075,30 +1075,32 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="J13" s="17"/>
+      <c r="O13" s="16"/>
+    </row>
+    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="C14" s="7"/>
       <c r="D14" s="8" t="s">
         <v>21</v>
       </c>
@@ -1109,20 +1111,22 @@
       <c r="J14" s="8"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="D15" s="8"/>
       <c r="G15" s="7"/>
       <c r="J15" s="8"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>97</v>
       </c>
@@ -1142,7 +1146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>98</v>
       </c>
@@ -1156,7 +1160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>38</v>
       </c>
@@ -1171,7 +1175,7 @@
       <c r="J18" s="8"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>40</v>
       </c>
@@ -1185,7 +1189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>42</v>
       </c>
@@ -1211,7 +1215,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>44</v>
       </c>
@@ -1221,7 +1225,7 @@
       <c r="J21" s="20"/>
       <c r="O21" s="19"/>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>45</v>
       </c>
@@ -1236,7 +1240,7 @@
       <c r="J22" s="8"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>47</v>
       </c>
@@ -1259,7 +1263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>49</v>
       </c>
@@ -1288,7 +1292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>51</v>
       </c>
@@ -1311,7 +1315,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
@@ -1340,7 +1344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>55</v>
       </c>
@@ -1373,7 +1377,7 @@
       </c>
       <c r="O27" s="7"/>
     </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>57</v>
       </c>
@@ -1391,7 +1395,7 @@
       <c r="J28" s="8"/>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>59</v>
       </c>
@@ -1409,7 +1413,7 @@
       <c r="J29" s="8"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>61</v>
       </c>
@@ -1424,7 +1428,7 @@
       <c r="J30" s="8"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>63</v>
       </c>
@@ -1435,7 +1439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>64</v>
       </c>
@@ -1458,7 +1462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>94</v>
       </c>
@@ -1493,7 +1497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
         <v>13</v>
       </c>
@@ -1510,7 +1514,7 @@
       <c r="J34" s="8"/>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
         <v>76</v>
       </c>
@@ -1524,7 +1528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>75</v>
       </c>
@@ -1544,7 +1548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>72</v>
       </c>
@@ -1558,7 +1562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>73</v>
       </c>
@@ -1584,7 +1588,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
         <v>74</v>
       </c>
@@ -1598,7 +1602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>79</v>
       </c>
@@ -1612,7 +1616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>81</v>
       </c>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AA5746-B9BD-436D-A158-71B6ED9CF5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC391E6-DD5B-45DE-A55A-5997675038E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
@@ -155,9 +155,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>Am Rand der Gemeinschaft</t>
-  </si>
-  <si>
     <t>7.1</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
   </si>
   <si>
     <t>6.2</t>
+  </si>
+  <si>
+    <t>Flucht</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
         <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>2</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N3" t="s">
         <v>21</v>
@@ -933,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="7"/>
       <c r="J7" s="8"/>
@@ -979,10 +979,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>21</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="E8" s="21"/>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>21</v>
@@ -1046,10 +1046,10 @@
         <v>29</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>21</v>
@@ -1080,7 +1080,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>21</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="8" t="s">
@@ -1113,7 +1113,7 @@
     </row>
     <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
@@ -1128,7 +1128,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
@@ -1137,7 +1137,7 @@
         <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>21</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -1165,7 +1165,7 @@
         <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>21</v>
@@ -1177,10 +1177,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>21</v>
@@ -1191,11 +1191,11 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
       <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="8" t="s">
@@ -1242,11 +1242,11 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
         <v>47</v>
       </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
       <c r="D23" s="10" t="s">
         <v>21</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M23" t="s">
         <v>21</v>
@@ -1265,11 +1265,11 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
         <v>49</v>
       </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
       <c r="D24" s="10" t="s">
         <v>21</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
         <v>21</v>
@@ -1294,11 +1294,11 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
         <v>51</v>
       </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
       <c r="D25" s="10" t="s">
         <v>21</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s">
         <v>21</v>
@@ -1317,11 +1317,11 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
         <v>53</v>
       </c>
-      <c r="B26" t="s">
-        <v>54</v>
-      </c>
       <c r="D26" s="10" t="s">
         <v>21</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
         <v>21</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8" t="s">
@@ -1359,7 +1359,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G27" s="7"/>
       <c r="I27" s="1" t="s">
@@ -1379,10 +1379,10 @@
     </row>
     <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>21</v>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
@@ -1430,10 +1430,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>21</v>
@@ -1441,13 +1441,13 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>21</v>
@@ -1464,16 +1464,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>21</v>
@@ -1502,7 +1502,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>21</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>21</v>
@@ -1530,13 +1530,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>21</v>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>21</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L38" t="s">
         <v>21</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>21</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
         <v>79</v>
-      </c>
-      <c r="B40" t="s">
-        <v>80</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>21</v>
@@ -1618,15 +1618,15 @@
     </row>
     <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="8"/>
       <c r="F41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>21</v>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC391E6-DD5B-45DE-A55A-5997675038E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31CB2C4-DD74-4546-84CE-3375AE156968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="98">
   <si>
     <t>Szene</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Thadden-Blech</t>
-  </si>
-  <si>
-    <t>Thadden Harmonists</t>
   </si>
   <si>
     <t>Tanz</t>
@@ -813,24 +810,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
-  <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="25"/>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="25"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" style="9"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -838,16 +835,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>2</v>
@@ -855,800 +852,812 @@
       <c r="H1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="8"/>
       <c r="G2" s="7"/>
-      <c r="O2" s="7"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I2" s="8"/>
+      <c r="K2" s="7"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I7" s="8"/>
+      <c r="J7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>67</v>
-      </c>
       <c r="C8" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="16"/>
-      <c r="J9" s="17"/>
-      <c r="O9" s="16"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I9" s="17"/>
+      <c r="K9" s="16"/>
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
       <c r="E12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="16"/>
-      <c r="J13" s="17"/>
-      <c r="O13" s="16"/>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="17"/>
+      <c r="K13" s="16"/>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="O14" s="7"/>
-    </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="8"/>
+      <c r="K14" s="7"/>
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="8"/>
       <c r="G15" s="7"/>
-      <c r="J15" s="8"/>
-      <c r="O15" s="7"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I15" s="8"/>
+      <c r="K15" s="7"/>
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="C17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="8"/>
       <c r="G18" s="7"/>
-      <c r="J18" s="8"/>
-      <c r="O18" s="7"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I18" s="8"/>
+      <c r="K18" s="7"/>
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
+      <c r="B20" t="s">
         <v>41</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
         <v>42</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>90</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
-        <v>43</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
       <c r="G21" s="19"/>
-      <c r="J21" s="20"/>
-      <c r="O21" s="19"/>
-    </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="20"/>
+      <c r="K21" s="19"/>
+      <c r="N21" s="19"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7"/>
-      <c r="J22" s="8"/>
-      <c r="O22" s="7"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I22" s="8"/>
+      <c r="K22" s="7"/>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>90</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="B27" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G27" s="7"/>
-      <c r="I27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="8"/>
+      <c r="I27" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="L27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="7"/>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" s="7"/>
-      <c r="J28" s="8"/>
-      <c r="O28" s="7"/>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="8"/>
+      <c r="K28" s="7"/>
+      <c r="N28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C29" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" s="7"/>
-      <c r="J29" s="8"/>
-      <c r="O29" s="7"/>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+      <c r="K29" s="7"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="7"/>
-      <c r="J30" s="8"/>
-      <c r="O30" s="7"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I30" s="8"/>
+      <c r="K30" s="7"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="D33" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
         <v>88</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
-        <v>89</v>
-      </c>
       <c r="G33" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="L33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="26">
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="I34" s="8"/>
+      <c r="K34" s="7"/>
+      <c r="N34" s="7"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="7"/>
-      <c r="J34" s="8"/>
-      <c r="O34" s="7"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
+      <c r="C35" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" t="s">
         <v>75</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="D37" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
+        <v>90</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
         <v>76</v>
       </c>
-      <c r="F36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s">
-        <v>91</v>
-      </c>
-      <c r="L38" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="D39" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="25" t="s">
+      <c r="B40" t="s">
         <v>78</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+      <c r="B41" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="8"/>
       <c r="F41" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="L41" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC391E6-DD5B-45DE-A55A-5997675038E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B03923-F499-4247-8A94-724424CA3299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="101">
   <si>
     <t>Szene</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>Flucht</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>Bin ich allein?</t>
   </si>
 </sst>
 </file>
@@ -450,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -479,6 +485,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -813,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="25"/>
@@ -1355,57 +1366,48 @@
       <c r="D27" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="7"/>
+      <c r="J27" s="8"/>
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="I27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="8"/>
-      <c r="L27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="7"/>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="J28" s="8"/>
-      <c r="O28" s="7"/>
+      <c r="G28" s="29"/>
+      <c r="I28" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="30"/>
+      <c r="L28" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" s="29"/>
     </row>
     <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="E29" s="1" t="s">
         <v>21</v>
       </c>
@@ -1415,239 +1417,257 @@
     </row>
     <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="7"/>
       <c r="J30" s="8"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>21</v>
-      </c>
+    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="J31" s="8"/>
+      <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" t="s">
-        <v>88</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="D34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
         <v>89</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26">
+      <c r="G34" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="26">
         <v>13</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="7"/>
-      <c r="J34" s="8"/>
-      <c r="O34" s="7"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" t="s">
-        <v>21</v>
-      </c>
+      <c r="C35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="J35" s="8"/>
+      <c r="O35" s="7"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" t="s">
-        <v>91</v>
-      </c>
-      <c r="L38" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>21</v>
       </c>
       <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>91</v>
+      </c>
+      <c r="L39" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>79</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+      <c r="D41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="F41" s="1" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
+      <c r="F42" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G41" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" s="8"/>
-      <c r="L41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" s="7" t="s">
+      <c r="G42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="8"/>
+      <c r="L42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" s="7" t="s">
         <v>21</v>
       </c>
     </row>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -456,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -485,11 +485,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1371,10 +1369,10 @@
       <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="29"/>
@@ -1384,7 +1382,7 @@
       <c r="E28" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" t="s">
         <v>91</v>
       </c>
       <c r="G28" s="29"/>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31CB2C4-DD74-4546-84CE-3375AE156968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FA67F5-5624-4328-951F-4B8FF4E68572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
@@ -336,7 +336,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +363,12 @@
       <sz val="9"/>
       <color rgb="FF36322C"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -447,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -459,10 +465,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -470,12 +472,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -813,7 +823,7 @@
   <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="25"/>
+    <col min="1" max="1" width="11.5546875" style="20"/>
     <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
@@ -828,7 +838,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -849,7 +859,7 @@
       <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="10" t="s">
@@ -872,7 +882,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="21" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -888,7 +898,7 @@
       <c r="N2" s="7"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="20" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
@@ -905,7 +915,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="20" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
@@ -919,7 +929,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="20" t="s">
         <v>17</v>
       </c>
       <c r="B5" t="s">
@@ -939,7 +949,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
@@ -950,16 +960,16 @@
       </c>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="21" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="2"/>
@@ -975,29 +985,29 @@
       <c r="N7" s="7"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="21"/>
+      <c r="C8" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="17"/>
       <c r="F8" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="23" t="s">
+      <c r="H8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>20</v>
       </c>
       <c r="K8" s="9" t="s">
@@ -1011,25 +1021,25 @@
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="21" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="30"/>
+      <c r="D9" s="31" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="K9" s="16"/>
-      <c r="N9" s="16"/>
+      <c r="G9" s="12"/>
+      <c r="I9" s="13"/>
+      <c r="K9" s="12"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="20" t="s">
         <v>27</v>
       </c>
       <c r="B10" t="s">
@@ -1040,10 +1050,10 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="19" t="s">
         <v>91</v>
       </c>
       <c r="F11" t="s">
@@ -1063,7 +1073,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="20" t="s">
         <v>31</v>
       </c>
       <c r="B12" t="s">
@@ -1074,33 +1084,33 @@
       </c>
     </row>
     <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="21" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="17"/>
+      <c r="C13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="13"/>
       <c r="E13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="K13" s="16"/>
-      <c r="N13" s="16"/>
+      <c r="G13" s="12"/>
+      <c r="I13" s="13"/>
+      <c r="K13" s="12"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="21" t="s">
         <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="25" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1112,23 +1122,23 @@
       <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="21" t="s">
         <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="8"/>
+      <c r="C15" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="25"/>
       <c r="G15" s="7"/>
       <c r="I15" s="8"/>
       <c r="K15" s="7"/>
       <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B16" t="s">
@@ -1143,7 +1153,7 @@
       <c r="G16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="23" t="s">
         <v>20</v>
       </c>
       <c r="N16" s="9" t="s">
@@ -1151,7 +1161,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="20" t="s">
         <v>96</v>
       </c>
       <c r="B17" t="s">
@@ -1165,7 +1175,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1181,7 +1191,7 @@
       <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B19" t="s">
@@ -1195,7 +1205,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="20" t="s">
         <v>40</v>
       </c>
       <c r="B20" t="s">
@@ -1220,19 +1230,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+    <row r="21" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="G21" s="19"/>
-      <c r="I21" s="20"/>
-      <c r="K21" s="19"/>
-      <c r="N21" s="19"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16"/>
+      <c r="G21" s="15"/>
+      <c r="I21" s="16"/>
+      <c r="K21" s="15"/>
+      <c r="N21" s="15"/>
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="21" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1248,7 +1258,7 @@
       <c r="N22" s="7"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="20" t="s">
         <v>45</v>
       </c>
       <c r="B23" t="s">
@@ -1271,7 +1281,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="20" t="s">
         <v>47</v>
       </c>
       <c r="B24" t="s">
@@ -1300,7 +1310,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="20" t="s">
         <v>49</v>
       </c>
       <c r="B25" t="s">
@@ -1323,7 +1333,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B26" t="s">
@@ -1352,7 +1362,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="21" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1384,7 +1394,7 @@
       <c r="N27" s="7"/>
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="21" t="s">
         <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1403,7 +1413,7 @@
       <c r="N28" s="7"/>
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1422,7 +1432,7 @@
       <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="21" t="s">
         <v>59</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1438,7 +1448,7 @@
       <c r="N30" s="7"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B31" t="s">
@@ -1449,10 +1459,10 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="19" t="s">
         <v>93</v>
       </c>
       <c r="F32" t="s">
@@ -1472,7 +1482,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="20" t="s">
         <v>92</v>
       </c>
       <c r="B33" t="s">
@@ -1507,7 +1517,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="26">
+      <c r="A34" s="21">
         <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1525,7 +1535,7 @@
       <c r="N34" s="7"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="20" t="s">
         <v>74</v>
       </c>
       <c r="B35" t="s">
@@ -1539,7 +1549,7 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="20" t="s">
         <v>73</v>
       </c>
       <c r="B36" t="s">
@@ -1559,7 +1569,7 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="20" t="s">
         <v>70</v>
       </c>
       <c r="B37" t="s">
@@ -1573,7 +1583,7 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B38" t="s">
@@ -1599,7 +1609,7 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="20" t="s">
         <v>72</v>
       </c>
       <c r="B39" t="s">
@@ -1613,7 +1623,7 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="20" t="s">
         <v>77</v>
       </c>
       <c r="B40" t="s">
@@ -1627,7 +1637,7 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="21" t="s">
         <v>79</v>
       </c>
       <c r="B41" s="1" t="s">

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B03923-F499-4247-8A94-724424CA3299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA30450-535D-4B59-BBEB-BBADFF99DB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="100">
   <si>
     <t>Szene</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Thadden-Blech</t>
-  </si>
-  <si>
-    <t>Thadden Harmonists</t>
   </si>
   <si>
     <t>Tanz</t>
@@ -456,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -488,6 +485,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -822,24 +820,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
-  <dimension ref="A1:O42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="25"/>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="25"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -847,16 +844,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>2</v>
@@ -864,809 +861,808 @@
       <c r="H1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="8"/>
       <c r="G2" s="7"/>
-      <c r="O2" s="7"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I2" s="8"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I7" s="8"/>
+      <c r="J7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>67</v>
-      </c>
       <c r="C8" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>20</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="16"/>
-      <c r="J9" s="17"/>
-      <c r="O9" s="16"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I9" s="17"/>
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
       <c r="E12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="17"/>
       <c r="E13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" s="16"/>
-      <c r="J13" s="17"/>
-      <c r="O13" s="16"/>
-    </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="17"/>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="J14" s="8"/>
-      <c r="O14" s="7"/>
-    </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="8"/>
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="8"/>
       <c r="G15" s="7"/>
-      <c r="J15" s="8"/>
-      <c r="O15" s="7"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I15" s="8"/>
+      <c r="N15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="C17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="8"/>
       <c r="G18" s="7"/>
-      <c r="J18" s="8"/>
-      <c r="O18" s="7"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I18" s="8"/>
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
+      <c r="B20" t="s">
         <v>41</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
         <v>42</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>90</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
-        <v>43</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
       <c r="G21" s="19"/>
-      <c r="J21" s="20"/>
-      <c r="O21" s="19"/>
-    </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="20"/>
+      <c r="N21" s="19"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7"/>
-      <c r="J22" s="8"/>
-      <c r="O22" s="7"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I22" s="8"/>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" t="s">
+        <v>89</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>90</v>
-      </c>
-      <c r="M23" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="B27" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" s="7"/>
-      <c r="J27" s="8"/>
-      <c r="O27" s="7"/>
-    </row>
-    <row r="28" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="8"/>
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
         <v>99</v>
-      </c>
-      <c r="B28" t="s">
-        <v>100</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G28" s="29"/>
-      <c r="I28" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="30"/>
-      <c r="L28" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="29"/>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="29"/>
+    </row>
+    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" s="7"/>
-      <c r="J29" s="8"/>
-      <c r="O29" s="7"/>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C30" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="7"/>
-      <c r="J30" s="8"/>
-      <c r="O30" s="7"/>
-    </row>
-    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I30" s="8"/>
+      <c r="N30" s="7"/>
+    </row>
+    <row r="31" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" s="7"/>
-      <c r="J31" s="8"/>
-      <c r="O31" s="7"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I31" s="8"/>
+      <c r="N31" s="7"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="D34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
         <v>88</v>
       </c>
-      <c r="G33" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" t="s">
-        <v>89</v>
-      </c>
       <c r="G34" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" t="s">
+        <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M34" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
         <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="I35" s="8"/>
+      <c r="N35" s="7"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="7"/>
-      <c r="J35" s="8"/>
-      <c r="O35" s="7"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
+      <c r="C36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
         <v>75</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="D38" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" t="s">
+        <v>90</v>
+      </c>
+      <c r="K39" t="s">
+        <v>20</v>
+      </c>
+      <c r="L39" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" t="s">
         <v>76</v>
       </c>
-      <c r="F37" t="s">
-        <v>87</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H37" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" t="s">
-        <v>91</v>
-      </c>
-      <c r="L39" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" t="s">
-        <v>21</v>
-      </c>
-      <c r="N39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="D40" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
+      <c r="B41" t="s">
         <v>78</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="B42" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="8"/>
       <c r="F42" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J42" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="L42" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA30450-535D-4B59-BBEB-BBADFF99DB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2818F56F-B45D-4BBA-A07C-4577156B34C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="100">
   <si>
     <t>Szene</t>
   </si>
@@ -311,9 +311,6 @@
     <t xml:space="preserve">Boyne </t>
   </si>
   <si>
-    <t> Eine Heldin A</t>
-  </si>
-  <si>
     <t>12.3</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>Bin ich allein?</t>
+  </si>
+  <si>
+    <t> Eine Heldin</t>
   </si>
 </sst>
 </file>
@@ -453,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -485,7 +485,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -821,22 +820,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="25"/>
-    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="25"/>
+    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -880,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>11</v>
       </c>
@@ -895,7 +894,7 @@
       <c r="I2" s="8"/>
       <c r="N2" s="7"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>12</v>
       </c>
@@ -912,7 +911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>16</v>
       </c>
@@ -926,7 +925,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
@@ -946,7 +945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
@@ -957,7 +956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>21</v>
       </c>
@@ -981,7 +980,7 @@
       </c>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>65</v>
       </c>
@@ -1017,7 +1016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
@@ -1034,7 +1033,7 @@
       <c r="I9" s="17"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -1045,12 +1044,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
         <v>87</v>
@@ -1058,6 +1057,9 @@
       <c r="G11" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
       <c r="K11" t="s">
         <v>20</v>
       </c>
@@ -1068,7 +1070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>31</v>
       </c>
@@ -1079,12 +1081,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>20</v>
@@ -1097,7 +1099,7 @@
       <c r="I13" s="17"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>82</v>
       </c>
@@ -1115,7 +1117,7 @@
       <c r="I14" s="8"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>81</v>
       </c>
@@ -1130,9 +1132,9 @@
       <c r="I15" s="8"/>
       <c r="N15" s="7"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -1146,16 +1148,16 @@
       <c r="G16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" t="s">
         <v>20</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1167,12 +1169,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>20</v>
@@ -1182,7 +1184,7 @@
       <c r="I18" s="8"/>
       <c r="N18" s="7"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>38</v>
       </c>
@@ -1196,7 +1198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>40</v>
       </c>
@@ -1222,7 +1224,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>42</v>
       </c>
@@ -1232,7 +1234,7 @@
       <c r="I21" s="20"/>
       <c r="N21" s="19"/>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>43</v>
       </c>
@@ -1247,7 +1249,7 @@
       <c r="I22" s="8"/>
       <c r="N22" s="7"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>45</v>
       </c>
@@ -1270,7 +1272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>47</v>
       </c>
@@ -1299,7 +1301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>49</v>
       </c>
@@ -1322,7 +1324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>51</v>
       </c>
@@ -1351,7 +1353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>53</v>
       </c>
@@ -1366,12 +1368,12 @@
       <c r="I27" s="8"/>
       <c r="N27" s="7"/>
     </row>
-    <row r="28" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" t="s">
         <v>98</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="30" t="s">
@@ -1392,7 +1394,7 @@
       </c>
       <c r="N28" s="29"/>
     </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>55</v>
       </c>
@@ -1410,7 +1412,7 @@
       <c r="I29" s="8"/>
       <c r="N29" s="7"/>
     </row>
-    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>57</v>
       </c>
@@ -1428,7 +1430,7 @@
       <c r="I30" s="8"/>
       <c r="N30" s="7"/>
     </row>
-    <row r="31" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>59</v>
       </c>
@@ -1443,7 +1445,7 @@
       <c r="I31" s="8"/>
       <c r="N31" s="7"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>61</v>
       </c>
@@ -1454,12 +1456,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
         <v>62</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F33" t="s">
         <v>87</v>
@@ -1467,6 +1469,9 @@
       <c r="G33" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
       <c r="K33" t="s">
         <v>20</v>
       </c>
@@ -1477,9 +1482,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
         <v>64</v>
@@ -1512,7 +1517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
         <v>13</v>
       </c>
@@ -1529,7 +1534,7 @@
       <c r="I35" s="8"/>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>74</v>
       </c>
@@ -1543,7 +1548,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>73</v>
       </c>
@@ -1563,7 +1568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>70</v>
       </c>
@@ -1577,7 +1582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
         <v>71</v>
       </c>
@@ -1603,7 +1608,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>72</v>
       </c>
@@ -1617,7 +1622,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
         <v>77</v>
       </c>
@@ -1631,7 +1636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>79</v>
       </c>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2818F56F-B45D-4BBA-A07C-4577156B34C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F96066F-453B-4C47-B5A1-60C32C291E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="108">
   <si>
     <t>Szene</t>
   </si>
@@ -128,9 +128,6 @@
     <t>Referat 1</t>
   </si>
   <si>
-    <t>Referat 2</t>
-  </si>
-  <si>
     <t>3.3</t>
   </si>
   <si>
@@ -140,12 +137,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Hitlergrußvermeidung</t>
-  </si>
-  <si>
-    <t>Irgendwo auf der Welt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schulinspektion </t>
   </si>
   <si>
@@ -161,9 +152,6 @@
     <t>7.2</t>
   </si>
   <si>
-    <t>Gesungener innerer Monolog</t>
-  </si>
-  <si>
     <t>Pause</t>
   </si>
   <si>
@@ -206,33 +194,18 @@
     <t>10</t>
   </si>
   <si>
-    <t>Zerbrechende und tragende Beziehungen</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
-    <t>Verrat</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
-    <t>Einfluss von außen</t>
-  </si>
-  <si>
     <t>12.1</t>
   </si>
   <si>
     <t>12.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Politische Akteure </t>
-  </si>
-  <si>
-    <t>Haß overload</t>
-  </si>
-  <si>
     <t>2.1</t>
   </si>
   <si>
@@ -266,9 +239,6 @@
     <t>Oh Haupt voll Blut und Wunden</t>
   </si>
   <si>
-    <t>Ringen um die Mitte</t>
-  </si>
-  <si>
     <t>13d</t>
   </si>
   <si>
@@ -287,9 +257,6 @@
     <t>5</t>
   </si>
   <si>
-    <t> Gemeinschaft: Heute</t>
-  </si>
-  <si>
     <t>Musikalische Leitung</t>
   </si>
   <si>
@@ -317,25 +284,82 @@
     <t>Kann Schule neutral sein?</t>
   </si>
   <si>
-    <t> Schlafsall Damals</t>
-  </si>
-  <si>
     <t>6.1</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>Flucht</t>
-  </si>
-  <si>
     <t>9.1</t>
   </si>
   <si>
     <t>Bin ich allein?</t>
   </si>
   <si>
-    <t> Eine Heldin</t>
+    <t>Aufstehen und Laut sein</t>
+  </si>
+  <si>
+    <t>Referat 2 und "Kleiner Zopf"</t>
+  </si>
+  <si>
+    <t> Schlafsaal Damals</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Irgendwo auf der Welt 1</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Irgendwo auf der Welt 2</t>
+  </si>
+  <si>
+    <t>Schalfsaal</t>
+  </si>
+  <si>
+    <t>Vorbereitung auf den Ball</t>
+  </si>
+  <si>
+    <t>Vorbereitung zur Flucht</t>
+  </si>
+  <si>
+    <t>Musikalischer Übergang</t>
+  </si>
+  <si>
+    <t>Innerer Monolog: Ich möchte leben</t>
+  </si>
+  <si>
+    <t>Sozial Media</t>
+  </si>
+  <si>
+    <t>Elisabeth wird verraten</t>
+  </si>
+  <si>
+    <t>Darf Schule neutral sein?</t>
+  </si>
+  <si>
+    <t>Wahlwerbung</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>Verratsszene</t>
+  </si>
+  <si>
+    <t>Tisch decken Barcoker Tanz mit übergang</t>
+  </si>
+  <si>
+    <t>Demonstration</t>
+  </si>
+  <si>
+    <t>Tanz um die Mitte</t>
   </si>
 </sst>
 </file>
@@ -453,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -485,6 +509,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -819,23 +858,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
-  <dimension ref="A1:N42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="25"/>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="25"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -848,38 +888,41 @@
       <c r="D1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
-        <v>32</v>
+      <c r="E1" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>11</v>
       </c>
@@ -890,11 +933,12 @@
         <v>20</v>
       </c>
       <c r="D2" s="8"/>
-      <c r="G2" s="7"/>
-      <c r="I2" s="8"/>
-      <c r="N2" s="7"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E2" s="38"/>
+      <c r="H2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>12</v>
       </c>
@@ -904,14 +948,14 @@
       <c r="C3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>16</v>
       </c>
@@ -921,11 +965,11 @@
       <c r="C4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
@@ -935,28 +979,28 @@
       <c r="C5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>21</v>
       </c>
@@ -969,23 +1013,24 @@
       <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="7"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E7" s="39"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>20</v>
@@ -993,20 +1038,18 @@
       <c r="D8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="21"/>
+      <c r="G8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="23" t="s">
         <v>20</v>
       </c>
       <c r="L8" t="s">
@@ -1015,8 +1058,11 @@
       <c r="M8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
@@ -1027,646 +1073,764 @@
       <c r="D9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3"/>
+      <c r="E9" s="41"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G9" s="3"/>
+      <c r="H9" s="16"/>
+      <c r="J9" s="17"/>
+      <c r="O9" s="16"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="F11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
+      <c r="C13" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="16"/>
+      <c r="J13" s="17"/>
+      <c r="O13" s="16"/>
+    </row>
+    <row r="14" spans="1:15" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="37"/>
+      <c r="F14"/>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="10"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="15" spans="1:15" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="37"/>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15"/>
+      <c r="H15" s="9"/>
+      <c r="I15"/>
+      <c r="J15" s="10"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15" s="9"/>
+    </row>
+    <row r="16" spans="1:15" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="37"/>
+      <c r="F16"/>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="10"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="38"/>
+      <c r="F17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="I13" s="17"/>
-      <c r="N13" s="16"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="C18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="38"/>
+      <c r="H18" s="7"/>
+      <c r="J18" s="8"/>
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="I14" s="8"/>
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="B19" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="43"/>
+      <c r="H19" s="35"/>
+      <c r="J19" s="36"/>
+      <c r="M19" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="35"/>
+    </row>
+    <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="G15" s="7"/>
-      <c r="I15" s="8"/>
-      <c r="N15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="B20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="38"/>
+      <c r="H20" s="7"/>
+      <c r="J20" s="8"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="B21" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
+      <c r="C21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="G18" s="7"/>
-      <c r="I18" s="8"/>
-      <c r="N18" s="7"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="L22" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="44"/>
+      <c r="H23" s="19"/>
+      <c r="J23" s="20"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
+      <c r="B24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C24" s="7"/>
+      <c r="D24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="H24" s="7"/>
+      <c r="J24" s="8"/>
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" t="s">
-        <v>20</v>
-      </c>
-      <c r="L20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="B25" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="G21" s="19"/>
-      <c r="I21" s="20"/>
-      <c r="N21" s="19"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="D25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B26" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="I22" s="8"/>
-      <c r="N22" s="7"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="D26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B27" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" t="s">
-        <v>89</v>
-      </c>
-      <c r="L23" t="s">
-        <v>20</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="D27" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B28" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="D28" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B29" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" t="s">
-        <v>87</v>
-      </c>
-      <c r="J25" t="s">
-        <v>20</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" t="s">
-        <v>20</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="7"/>
-      <c r="I27" s="8"/>
-      <c r="N27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="29"/>
-      <c r="I28" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="N28" s="29"/>
-    </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="7"/>
-      <c r="I29" s="8"/>
-      <c r="N29" s="7"/>
-    </row>
-    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="7"/>
-      <c r="I30" s="8"/>
-      <c r="N30" s="7"/>
-    </row>
-    <row r="31" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="38"/>
+      <c r="H29" s="7"/>
+      <c r="J29" s="8"/>
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="29"/>
+      <c r="D30" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="45"/>
+      <c r="F30" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="J30" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30" s="29"/>
+    </row>
+    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="7"/>
-      <c r="I31" s="8"/>
-      <c r="N31" s="7"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="E31" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="J31" s="8"/>
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="J32" s="8"/>
+      <c r="O32" s="7"/>
+    </row>
+    <row r="33" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="36"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="35"/>
+      <c r="J33" s="36"/>
+      <c r="M33" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="35"/>
+    </row>
+    <row r="34" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="36"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="35"/>
+      <c r="J34" s="36"/>
+      <c r="O34" s="35"/>
+    </row>
+    <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="H35" s="7"/>
+      <c r="J35" s="8"/>
+      <c r="O35" s="7"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s">
+        <v>20</v>
+      </c>
+      <c r="L37" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="26">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="38"/>
+      <c r="H39" s="7"/>
+      <c r="J39" s="8"/>
+      <c r="O39" s="7"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>79</v>
+      </c>
+      <c r="L43" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43" t="s">
+        <v>20</v>
+      </c>
+      <c r="N43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="F33" t="s">
-        <v>87</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" t="s">
-        <v>20</v>
-      </c>
-      <c r="M34" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26">
-        <v>13</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" t="s">
+        <v>20</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="7"/>
-      <c r="I35" s="8"/>
-      <c r="N35" s="7"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="25" t="s">
+      <c r="B45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="38"/>
+      <c r="G46" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B36" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" t="s">
-        <v>86</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" t="s">
-        <v>90</v>
-      </c>
-      <c r="K39" t="s">
-        <v>20</v>
-      </c>
-      <c r="L39" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="F42" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N42" s="7" t="s">
+      <c r="H46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" s="7" t="s">
         <v>20</v>
       </c>
     </row>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F96066F-453B-4C47-B5A1-60C32C291E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EA40CE-E991-494B-AE9F-A5503A1A86C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -236,9 +236,6 @@
     <t>13a-1</t>
   </si>
   <si>
-    <t>Oh Haupt voll Blut und Wunden</t>
-  </si>
-  <si>
     <t>13d</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>Tanz um die Mitte</t>
+  </si>
+  <si>
+    <t>Mach End o Herr mach Ende</t>
   </si>
 </sst>
 </file>
@@ -477,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -509,21 +509,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -859,23 +844,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
   <dimension ref="A1:O46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="25"/>
-    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="25"/>
+    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -888,14 +873,14 @@
       <c r="D1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="33" t="s">
-        <v>98</v>
+      <c r="E1" t="s">
+        <v>97</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
@@ -922,7 +907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>11</v>
       </c>
@@ -933,12 +918,11 @@
         <v>20</v>
       </c>
       <c r="D2" s="8"/>
-      <c r="E2" s="38"/>
       <c r="H2" s="7"/>
       <c r="J2" s="8"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>12</v>
       </c>
@@ -949,13 +933,13 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>16</v>
       </c>
@@ -969,7 +953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
@@ -980,7 +964,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>20</v>
@@ -989,7 +973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
@@ -1000,7 +984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>21</v>
       </c>
@@ -1013,10 +997,10 @@
       <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7" s="7"/>
       <c r="J7" s="8"/>
@@ -1025,7 +1009,7 @@
       </c>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>56</v>
       </c>
@@ -1038,10 +1022,10 @@
       <c r="D8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>20</v>
@@ -1062,7 +1046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
@@ -1073,14 +1057,14 @@
       <c r="D9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="41"/>
+      <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="16"/>
       <c r="J9" s="17"/>
       <c r="O9" s="16"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
@@ -1091,15 +1075,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1117,12 +1101,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
         <v>20</v>
@@ -1131,18 +1115,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="17"/>
-      <c r="E13" s="42"/>
       <c r="F13" s="4" t="s">
         <v>20</v>
       </c>
@@ -1150,103 +1133,74 @@
       <c r="J13" s="17"/>
       <c r="O13" s="16"/>
     </row>
-    <row r="14" spans="1:15" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="32" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="37"/>
-      <c r="F14"/>
-      <c r="G14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="10"/>
-      <c r="K14"/>
-      <c r="L14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14" s="9"/>
-    </row>
-    <row r="15" spans="1:15" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="37"/>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15"/>
-      <c r="H15" s="9"/>
-      <c r="I15"/>
-      <c r="J15" s="10"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15" s="9"/>
-    </row>
-    <row r="16" spans="1:15" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="37"/>
-      <c r="F16"/>
-      <c r="G16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="38"/>
       <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1254,9 +1208,9 @@
       <c r="J17" s="8"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>33</v>
@@ -1265,47 +1219,40 @@
         <v>20</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="38"/>
       <c r="H18" s="7"/>
       <c r="J18" s="8"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="43"/>
-      <c r="H19" s="35"/>
-      <c r="J19" s="36"/>
-      <c r="M19" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="O19" s="35"/>
-    </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="38"/>
       <c r="H20" s="7"/>
       <c r="J20" s="8"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>35</v>
       </c>
@@ -1319,12 +1266,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>20</v>
@@ -1333,7 +1280,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1345,18 +1292,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="44"/>
       <c r="H23" s="19"/>
       <c r="J23" s="20"/>
       <c r="O23" s="19"/>
     </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>39</v>
       </c>
@@ -1367,12 +1313,11 @@
       <c r="D24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="38"/>
       <c r="H24" s="7"/>
       <c r="J24" s="8"/>
       <c r="O24" s="7"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>41</v>
       </c>
@@ -1386,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M25" t="s">
         <v>20</v>
@@ -1395,7 +1340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>43</v>
       </c>
@@ -1409,7 +1354,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
@@ -1424,7 +1369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
         <v>45</v>
       </c>
@@ -1438,7 +1383,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K27" t="s">
         <v>20</v>
@@ -1447,7 +1392,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>47</v>
       </c>
@@ -1461,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s">
         <v>20</v>
@@ -1473,7 +1418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>49</v>
       </c>
@@ -1484,28 +1429,26 @@
       <c r="D29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="38"/>
       <c r="H29" s="7"/>
       <c r="J29" s="8"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
         <v>83</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="45"/>
       <c r="F30" s="28" t="s">
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H30" s="29"/>
       <c r="J30" s="30" t="s">
@@ -1516,36 +1459,35 @@
       </c>
       <c r="O30" s="29"/>
     </row>
-    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>51</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="7"/>
       <c r="J31" s="8"/>
       <c r="O31" s="7"/>
     </row>
-    <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
         <v>52</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="8"/>
-      <c r="E32" s="38"/>
       <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
@@ -1553,83 +1495,72 @@
       <c r="J32" s="8"/>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="32" t="s">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="35"/>
-      <c r="J33" s="36"/>
-      <c r="M33" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="O33" s="35"/>
-    </row>
-    <row r="34" spans="1:15" s="34" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="32" t="s">
+      <c r="B34" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="36"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="35"/>
-      <c r="J34" s="36"/>
-      <c r="O34" s="35"/>
-    </row>
-    <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
         <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="38"/>
       <c r="H35" s="7"/>
       <c r="J35" s="8"/>
       <c r="O35" s="7"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>55</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>20</v>
@@ -1647,20 +1578,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="33" t="s">
+      <c r="E38" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
         <v>20</v>
       </c>
       <c r="I38" t="s">
@@ -1670,7 +1601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26">
         <v>13</v>
       </c>
@@ -1683,12 +1614,11 @@
       <c r="D39" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="38"/>
       <c r="H39" s="7"/>
       <c r="J39" s="8"/>
       <c r="O39" s="7"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>65</v>
       </c>
@@ -1702,15 +1632,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>20</v>
@@ -1722,7 +1652,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
         <v>61</v>
       </c>
@@ -1736,7 +1666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
         <v>62</v>
       </c>
@@ -1750,7 +1680,7 @@
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -1762,17 +1692,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="33" t="s">
+      <c r="E44" t="s">
         <v>20</v>
       </c>
       <c r="M44" t="s">
@@ -1785,32 +1715,31 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
         <v>67</v>
       </c>
-      <c r="B45" t="s">
+      <c r="D45" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D45" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="26" t="s">
+      <c r="B46" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="38"/>
       <c r="G46" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>20</v>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EA40CE-E991-494B-AE9F-A5503A1A86C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EA4871-61A9-41D1-9F89-E7D6B3541684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
@@ -221,21 +221,9 @@
     <t xml:space="preserve">Dystopie </t>
   </si>
   <si>
-    <t>13b-1</t>
-  </si>
-  <si>
-    <t>13b-2</t>
-  </si>
-  <si>
     <t>13c</t>
   </si>
   <si>
-    <t>13a-2</t>
-  </si>
-  <si>
-    <t>13a-1</t>
-  </si>
-  <si>
     <t>13d</t>
   </si>
   <si>
@@ -360,6 +348,18 @@
   </si>
   <si>
     <t>Mach End o Herr mach Ende</t>
+  </si>
+  <si>
+    <t>13a.1</t>
+  </si>
+  <si>
+    <t>13a.2</t>
+  </si>
+  <si>
+    <t>13b.1</t>
+  </si>
+  <si>
+    <t>13b.2</t>
   </si>
 </sst>
 </file>
@@ -874,13 +874,13 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
@@ -933,7 +933,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N3" t="s">
         <v>20</v>
@@ -964,7 +964,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>20</v>
@@ -1000,7 +1000,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H7" s="7"/>
       <c r="J7" s="8"/>
@@ -1025,7 +1025,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>20</v>
@@ -1080,10 +1080,10 @@
         <v>28</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1106,7 +1106,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
         <v>20</v>
@@ -1120,7 +1120,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>20</v>
@@ -1135,16 +1135,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>20</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
         <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>92</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>20</v>
@@ -1169,16 +1169,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="8" t="s">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>33</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>20</v>
@@ -1242,7 +1242,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>20</v>
@@ -1271,7 +1271,7 @@
         <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>20</v>
@@ -1280,7 +1280,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
         <v>20</v>
@@ -1354,7 +1354,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
@@ -1383,7 +1383,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K27" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I28" t="s">
         <v>20</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="30" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="30" t="s">
@@ -1448,7 +1448,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H30" s="29"/>
       <c r="J30" s="30" t="s">
@@ -1464,7 +1464,7 @@
         <v>51</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8" t="s">
@@ -1482,7 +1482,7 @@
         <v>52</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>20</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>20</v>
@@ -1531,7 +1531,7 @@
         <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="8" t="s">
@@ -1546,7 +1546,7 @@
         <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>20</v>
@@ -1557,10 +1557,10 @@
         <v>55</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>20</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>20</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
         <v>59</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>20</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="B42" t="s">
         <v>60</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
@@ -1680,7 +1680,7 @@
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>20</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>20</v>
@@ -1731,15 +1731,15 @@
     </row>
     <row r="46" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="8"/>
       <c r="G46" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>20</v>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EA4871-61A9-41D1-9F89-E7D6B3541684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961D446E-B326-4352-8077-EDF0B85B8033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
@@ -188,9 +188,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Innerer Konflikt der „modernen Elisabeth“ </t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>13b.2</t>
+  </si>
+  <si>
+    <t>Nach dem Ball (Verarbeitung der Trennung)</t>
   </si>
 </sst>
 </file>
@@ -847,7 +847,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="25"/>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -874,13 +874,13 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
         <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
@@ -933,7 +933,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
         <v>20</v>
@@ -964,7 +964,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>20</v>
@@ -1000,7 +1000,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H7" s="7"/>
       <c r="J7" s="8"/>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>56</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>57</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>20</v>
@@ -1025,7 +1025,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>20</v>
@@ -1080,10 +1080,10 @@
         <v>28</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>20</v>
@@ -1106,7 +1106,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
         <v>20</v>
@@ -1120,7 +1120,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>20</v>
@@ -1135,16 +1135,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>20</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>20</v>
@@ -1169,16 +1169,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" t="s">
-        <v>87</v>
-      </c>
       <c r="C16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="8" t="s">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>33</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>20</v>
@@ -1242,7 +1242,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>20</v>
@@ -1271,7 +1271,7 @@
         <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>20</v>
@@ -1280,7 +1280,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M25" t="s">
         <v>20</v>
@@ -1354,7 +1354,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
@@ -1383,7 +1383,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K27" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I28" t="s">
         <v>20</v>
@@ -1423,7 +1423,7 @@
         <v>49</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="8" t="s">
@@ -1435,10 +1435,10 @@
     </row>
     <row r="30" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
         <v>78</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="30" t="s">
@@ -1448,7 +1448,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H30" s="29"/>
       <c r="J30" s="30" t="s">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8" t="s">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>20</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
         <v>98</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>20</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="8" t="s">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>20</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>20</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>20</v>
@@ -1606,7 +1606,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>20</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>20</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>20</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>20</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
@@ -1680,7 +1680,7 @@
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>20</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
         <v>62</v>
-      </c>
-      <c r="B45" t="s">
-        <v>63</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>20</v>
@@ -1731,15 +1731,15 @@
     </row>
     <row r="46" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="8"/>
       <c r="G46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>20</v>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961D446E-B326-4352-8077-EDF0B85B8033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74584BE-AB6F-4E64-88D7-6F6F27058D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="106">
   <si>
     <t>Szene</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Tanz</t>
   </si>
   <si>
-    <t>Schuleröffnung</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -137,9 +134,6 @@
     <t>4</t>
   </si>
   <si>
-    <t xml:space="preserve">Schulinspektion </t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
@@ -167,21 +161,12 @@
     <t>2nd Walz</t>
   </si>
   <si>
-    <t>8.2</t>
-  </si>
-  <si>
     <t>Mambo</t>
   </si>
   <si>
-    <t>8.3</t>
-  </si>
-  <si>
     <t>Tanzparty</t>
   </si>
   <si>
-    <t>8.4</t>
-  </si>
-  <si>
     <t>Eskalation</t>
   </si>
   <si>
@@ -197,12 +182,6 @@
     <t>12</t>
   </si>
   <si>
-    <t>12.1</t>
-  </si>
-  <si>
-    <t>12.2</t>
-  </si>
-  <si>
     <t>2.1</t>
   </si>
   <si>
@@ -218,18 +197,9 @@
     <t xml:space="preserve">Dystopie </t>
   </si>
   <si>
-    <t>13c</t>
-  </si>
-  <si>
-    <t>13d</t>
-  </si>
-  <si>
     <t>Mögliches Happy End</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>Finale</t>
   </si>
   <si>
@@ -260,18 +230,12 @@
     <t xml:space="preserve">Boyne </t>
   </si>
   <si>
-    <t>12.3</t>
-  </si>
-  <si>
     <t>Kann Schule neutral sein?</t>
   </si>
   <si>
     <t>6.1</t>
   </si>
   <si>
-    <t>9.1</t>
-  </si>
-  <si>
     <t>Bin ich allein?</t>
   </si>
   <si>
@@ -308,9 +272,6 @@
     <t>Vorbereitung zur Flucht</t>
   </si>
   <si>
-    <t>Musikalischer Übergang</t>
-  </si>
-  <si>
     <t>Innerer Monolog: Ich möchte leben</t>
   </si>
   <si>
@@ -347,19 +308,52 @@
     <t>Mach End o Herr mach Ende</t>
   </si>
   <si>
-    <t>13a.1</t>
-  </si>
-  <si>
-    <t>13a.2</t>
-  </si>
-  <si>
-    <t>13b.1</t>
-  </si>
-  <si>
-    <t>13b.2</t>
-  </si>
-  <si>
-    <t>Nach dem Ball (Verarbeitung der Trennung)</t>
+    <t>Osterfeier</t>
+  </si>
+  <si>
+    <t>Nach dem Ball</t>
+  </si>
+  <si>
+    <t>Gestapo in Tuzingen</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>12a.1</t>
+  </si>
+  <si>
+    <t>12a.2</t>
+  </si>
+  <si>
+    <t>12b.1</t>
+  </si>
+  <si>
+    <t>12b.2</t>
+  </si>
+  <si>
+    <t>12c</t>
+  </si>
+  <si>
+    <t>12d</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
 </sst>
 </file>
@@ -396,7 +390,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,6 +406,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -509,6 +509,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -841,9 +845,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{71E547F6-03DB-45A4-8800-2182588C5808}">
+  <we:reference id="WA200010215" version="2.0.0.0" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010215" version="2.0.0.0" store="WA200010215" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="bps.codex_control.document_id" value="&quot;31676971-55d2-40c7-89c4-ed23e1dc6e0f&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="25"/>
@@ -868,19 +894,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="E1" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
@@ -909,13 +935,13 @@
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="8"/>
       <c r="H2" s="7"/>
@@ -924,138 +950,138 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H7" s="7"/>
       <c r="J7" s="8"/>
       <c r="K7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1066,68 +1092,68 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="17"/>
       <c r="F13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" s="16"/>
       <c r="J13" s="17"/>
@@ -1135,74 +1161,74 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" s="7"/>
       <c r="J17" s="8"/>
@@ -1210,13 +1236,13 @@
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="8"/>
       <c r="H18" s="7"/>
@@ -1225,542 +1251,513 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="J20" s="8"/>
-      <c r="O20" s="7"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="C19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="H21" s="19"/>
+      <c r="J21" s="20"/>
+      <c r="O21" s="19"/>
+    </row>
+    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23" t="s">
+        <v>19</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" t="s">
-        <v>72</v>
-      </c>
-      <c r="L22" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" t="s">
-        <v>20</v>
-      </c>
-      <c r="N22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20"/>
-      <c r="H23" s="19"/>
-      <c r="J23" s="20"/>
-      <c r="O23" s="19"/>
-    </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="J24" s="8"/>
-      <c r="O24" s="7"/>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s">
+        <v>19</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>72</v>
-      </c>
-      <c r="M25" t="s">
-        <v>20</v>
+        <v>60</v>
+      </c>
+      <c r="K25" t="s">
+        <v>19</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" t="s">
         <v>43</v>
       </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" t="s">
-        <v>70</v>
-      </c>
-      <c r="K27" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>20</v>
-      </c>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="F27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="J27" s="8"/>
+      <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>20</v>
+        <v>86</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" t="s">
-        <v>70</v>
-      </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" t="s">
-        <v>20</v>
-      </c>
-      <c r="O28" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="J29" s="8"/>
-      <c r="O29" s="7"/>
-    </row>
-    <row r="30" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" s="29"/>
-      <c r="J30" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L30" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="O30" s="29"/>
-    </row>
-    <row r="31" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="J30" s="8"/>
+      <c r="O30" s="7"/>
+    </row>
+    <row r="31" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" s="29"/>
+      <c r="J31" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31" s="29"/>
+    </row>
+    <row r="32" spans="1:15" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="7"/>
-      <c r="J31" s="8"/>
-      <c r="O31" s="7"/>
-    </row>
-    <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="F32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="7"/>
-      <c r="J32" s="8"/>
-      <c r="O32" s="7"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" t="s">
-        <v>20</v>
-      </c>
+      <c r="C32" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="34"/>
+      <c r="F32" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="33"/>
+      <c r="J32" s="34"/>
+      <c r="O32" s="33"/>
+    </row>
+    <row r="33" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="J33" s="8"/>
+      <c r="O33" s="7"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="7"/>
-      <c r="J35" s="8"/>
-      <c r="O35" s="7"/>
+        <v>82</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" t="s">
+        <v>19</v>
+      </c>
+      <c r="M35" t="s">
+        <v>19</v>
+      </c>
+      <c r="N35" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G37" t="s">
-        <v>70</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" t="s">
-        <v>20</v>
-      </c>
-      <c r="L37" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" t="s">
-        <v>20</v>
-      </c>
-      <c r="N37" t="s">
-        <v>20</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="J37" s="8"/>
+      <c r="O37" s="7"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26">
-        <v>13</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H39" s="7"/>
-      <c r="J39" s="8"/>
-      <c r="O39" s="7"/>
+      <c r="B39" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>20</v>
+        <v>52</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>18</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>69</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>20</v>
+        <v>63</v>
+      </c>
+      <c r="L41" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" t="s">
+        <v>19</v>
+      </c>
+      <c r="N41" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="M42" t="s">
+        <v>19</v>
+      </c>
+      <c r="N42" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
-        <v>73</v>
-      </c>
-      <c r="L43" t="s">
-        <v>20</v>
-      </c>
-      <c r="M43" t="s">
-        <v>20</v>
-      </c>
-      <c r="N43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="M44" t="s">
-        <v>20</v>
-      </c>
-      <c r="N44" t="s">
-        <v>20</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="G46" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O46" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="8"/>
+      <c r="G44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O44" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/besetzung.xlsx
+++ b/besetzung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thadden27\thadden27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\thadden27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74584BE-AB6F-4E64-88D7-6F6F27058D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0D39D-5D34-4E0C-B484-DB3499A4EFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{870A77A3-6497-424F-BFDB-56D4CBDBF5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="103">
   <si>
     <t>Szene</t>
   </si>
@@ -191,9 +191,6 @@
     <t>Multible Enden</t>
   </si>
   <si>
-    <t>Ermordung Elisabeth v. Thadden</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dystopie </t>
   </si>
   <si>
@@ -305,9 +302,6 @@
     <t>Tanz um die Mitte</t>
   </si>
   <si>
-    <t>Mach End o Herr mach Ende</t>
-  </si>
-  <si>
     <t>Osterfeier</t>
   </si>
   <si>
@@ -335,25 +329,22 @@
     <t>11.3</t>
   </si>
   <si>
-    <t>12a.1</t>
-  </si>
-  <si>
-    <t>12a.2</t>
-  </si>
-  <si>
-    <t>12b.1</t>
-  </si>
-  <si>
-    <t>12b.2</t>
-  </si>
-  <si>
-    <t>12c</t>
-  </si>
-  <si>
-    <t>12d</t>
-  </si>
-  <si>
     <t>13</t>
+  </si>
+  <si>
+    <t>Ermordung Elisabeth "Mach End o Herr"</t>
+  </si>
+  <si>
+    <t>12.1</t>
+  </si>
+  <si>
+    <t>12.2</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>12.4</t>
   </si>
 </sst>
 </file>
@@ -477,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -513,6 +504,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -869,24 +861,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EAA9A49-82B2-433C-BF39-5078DFD427BF}">
-  <dimension ref="A1:O44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="25"/>
-    <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="25"/>
+    <col min="2" max="2" width="40.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -900,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
         <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
@@ -933,12 +925,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
@@ -948,7 +940,7 @@
       <c r="J2" s="8"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>11</v>
       </c>
@@ -959,13 +951,13 @@
         <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>15</v>
       </c>
@@ -979,7 +971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>16</v>
       </c>
@@ -990,7 +982,7 @@
         <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>19</v>
@@ -999,7 +991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>17</v>
       </c>
@@ -1010,7 +1002,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>20</v>
       </c>
@@ -1026,7 +1018,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H7" s="7"/>
       <c r="J7" s="8"/>
@@ -1035,7 +1027,7 @@
       </c>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
         <v>48</v>
       </c>
@@ -1051,7 +1043,7 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>19</v>
@@ -1072,7 +1064,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>22</v>
       </c>
@@ -1090,7 +1082,7 @@
       <c r="J9" s="17"/>
       <c r="O9" s="16"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>26</v>
       </c>
@@ -1101,15 +1093,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>19</v>
@@ -1127,12 +1119,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -1141,12 +1133,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>19</v>
@@ -1159,69 +1151,69 @@
       <c r="J13" s="17"/>
       <c r="O13" s="16"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O16" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="8" t="s">
@@ -1234,12 +1226,12 @@
       <c r="J17" s="8"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -1249,9 +1241,9 @@
       <c r="J18" s="8"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
@@ -1263,12 +1255,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>19</v>
@@ -1277,7 +1269,7 @@
         <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L20" t="s">
         <v>19</v>
@@ -1289,7 +1281,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>36</v>
       </c>
@@ -1299,7 +1291,7 @@
       <c r="J21" s="20"/>
       <c r="O21" s="19"/>
     </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
         <v>32</v>
       </c>
@@ -1314,7 +1306,7 @@
       <c r="J22" s="8"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="25" t="s">
         <v>33</v>
       </c>
@@ -1328,7 +1320,7 @@
         <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M23" t="s">
         <v>19</v>
@@ -1337,7 +1329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
         <v>35</v>
       </c>
@@ -1351,7 +1343,7 @@
         <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
         <v>19</v>
@@ -1366,9 +1358,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
@@ -1380,7 +1372,7 @@
         <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K25" t="s">
         <v>19</v>
@@ -1389,9 +1381,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
@@ -1403,7 +1395,7 @@
         <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I26" t="s">
         <v>19</v>
@@ -1415,12 +1407,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>19</v>
@@ -1433,12 +1425,12 @@
       <c r="J27" s="8"/>
       <c r="O27" s="7"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>19</v>
@@ -1450,12 +1442,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>19</v>
@@ -1464,12 +1456,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
@@ -1479,12 +1471,12 @@
       <c r="J30" s="8"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="25" t="s">
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="30" t="s">
@@ -1494,7 +1486,7 @@
         <v>19</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H31" s="29"/>
       <c r="J31" s="30" t="s">
@@ -1505,12 +1497,12 @@
       </c>
       <c r="O31" s="29"/>
     </row>
-    <row r="32" spans="1:15" s="32" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" s="32" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="31" t="s">
         <v>45</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C32" s="33" t="s">
         <v>19</v>
@@ -1523,12 +1515,12 @@
       <c r="J32" s="34"/>
       <c r="O32" s="33"/>
     </row>
-    <row r="33" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="26" t="s">
         <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="8" t="s">
@@ -1538,26 +1530,26 @@
       <c r="J33" s="8"/>
       <c r="O33" s="7"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
-        <v>84</v>
-      </c>
       <c r="B35" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>19</v>
@@ -1575,12 +1567,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>19</v>
@@ -1598,7 +1590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="26" t="s">
         <v>47</v>
       </c>
@@ -1615,12 +1607,12 @@
       <c r="J37" s="8"/>
       <c r="O37" s="7"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>19</v>
@@ -1628,47 +1620,62 @@
       <c r="F38" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G38" t="s">
+        <v>58</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
         <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
-      </c>
-      <c r="G39" t="s">
-        <v>59</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>101</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F40" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="M40" t="s">
+        <v>19</v>
+      </c>
+      <c r="N40" t="s">
+        <v>19</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>19</v>
@@ -1676,87 +1683,38 @@
       <c r="F41" t="s">
         <v>19</v>
       </c>
-      <c r="G41" t="s">
-        <v>63</v>
-      </c>
-      <c r="L41" t="s">
-        <v>19</v>
-      </c>
-      <c r="M41" t="s">
-        <v>19</v>
-      </c>
-      <c r="N41" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" t="s">
-        <v>19</v>
-      </c>
-      <c r="M42" t="s">
-        <v>19</v>
-      </c>
-      <c r="N42" t="s">
-        <v>19</v>
-      </c>
-      <c r="O42" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" t="s">
+    </row>
+    <row r="42" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="G44" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O44" s="7" t="s">
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
+      <c r="G42" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="7" t="s">
         <v>19</v>
       </c>
     </row>
